--- a/CRSP.xlsx
+++ b/CRSP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435207FF-6B0B-4F51-BDF5-3D9B333FB5D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1B54DE-5BB4-40B3-B40A-96892A0BC84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37710" yWindow="0" windowWidth="29955" windowHeight="19170" xr2:uid="{1C79B58B-B82D-44F0-B2E8-82D243545AE2}"/>
+    <workbookView xWindow="3800" yWindow="3800" windowWidth="22360" windowHeight="16580" xr2:uid="{1C79B58B-B82D-44F0-B2E8-82D243545AE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="83">
   <si>
     <t>Price</t>
   </si>
@@ -193,9 +193,6 @@
     <t>Split</t>
   </si>
   <si>
-    <t>Q224</t>
-  </si>
-  <si>
     <t>PIC</t>
   </si>
   <si>
@@ -208,9 +205,6 @@
     <t>Approved</t>
   </si>
   <si>
-    <t>CTX112</t>
-  </si>
-  <si>
     <t>CTX211</t>
   </si>
   <si>
@@ -260,6 +254,39 @@
   </si>
   <si>
     <t>Allogeneic</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t>Samarth Kulkarni</t>
+  </si>
+  <si>
+    <t>CTX460</t>
+  </si>
+  <si>
+    <t>AATD</t>
+  </si>
+  <si>
+    <t>SERPINA1</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>CTX321</t>
+  </si>
+  <si>
+    <t>CTX611</t>
+  </si>
+  <si>
+    <t>CTX112 (Zugocabtagene geleucel)</t>
+  </si>
+  <si>
+    <t>SLE, SSc, IM, ITP, wAIHA, PMS, NMOSD, MOGAD, NMDAR, LGI1 AIE, SPS</t>
   </si>
 </sst>
 </file>
@@ -396,27 +423,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -735,261 +770,333 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD17C675-368D-4950-ACC1-F92026601A1F}">
   <dimension ref="B2:M18"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.7265625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="14.54296875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="12.7265625" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="8.7265625" style="10"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11">
+        <v>62.4</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="13"/>
+      <c r="K3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="14">
+        <v>96.448791999999997</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="13"/>
+      <c r="K4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="14">
+        <f>L2*L3</f>
+        <v>6018.4046208</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="13"/>
+      <c r="K5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="14">
+        <f>423.308+2018.477</f>
+        <v>2441.7849999999999</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="13"/>
+      <c r="K6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="10">
+        <v>585.47</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="13"/>
+      <c r="K7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="14">
+        <f>L4-L5+L6</f>
+        <v>4162.0896208000004</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="13"/>
+      <c r="L8" s="14"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="13"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="3"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="4"/>
+      <c r="K10" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10" s="14">
+        <v>3223.924</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="1">
-        <v>47.01</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B3" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="8"/>
-      <c r="K3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2">
-        <v>85.168158000000005</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="8"/>
-      <c r="K4" t="s">
-        <v>2</v>
-      </c>
-      <c r="L4" s="2">
-        <f>L2*L3</f>
-        <v>4003.7551075800002</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="8"/>
-      <c r="K5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L5" s="2">
-        <f>484.472+1517.147+11.216</f>
-        <v>2012.8349999999998</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H6" s="8"/>
-      <c r="K6" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="8"/>
-      <c r="K7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L7" s="2">
-        <f>L4-L5+L6</f>
-        <v>1990.9201075800004</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="H8" s="8"/>
-      <c r="L8" s="16"/>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B9" s="7" t="s">
+      <c r="C11" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="8"/>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="6"/>
-      <c r="K10" t="s">
+      <c r="D11" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="22"/>
+      <c r="H11" s="13"/>
+      <c r="K11" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="L10" s="2">
-        <v>3223.924</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B11" s="17" t="s">
+      <c r="L11" s="14">
+        <v>1242.6990000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="15" t="s">
+      <c r="G12" s="22"/>
+      <c r="H12" s="13"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="22"/>
+      <c r="H13" s="13"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="13"/>
+      <c r="K14" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="8"/>
-      <c r="K11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1242.6990000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B12" s="7" t="s">
+      <c r="L14" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12" s="8"/>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B13" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B14" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="G15" s="22"/>
+      <c r="H15" s="13"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="22"/>
+      <c r="F16" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" s="22"/>
+      <c r="H16" s="13"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H14" s="8"/>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B15" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="8"/>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B16" s="7"/>
-      <c r="H16" s="8"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="7"/>
-      <c r="H17" s="8"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" s="9"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="11"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" s="22"/>
+      <c r="H17" s="13"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="17"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="19"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1002,18 +1109,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BECE7A04-E8B2-4A4A-BE68-37D0156A559F}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>7</v>
       </c>
@@ -1021,7 +1128,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>20</v>
       </c>
@@ -1029,7 +1136,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>10</v>
       </c>
@@ -1037,7 +1144,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>11</v>
       </c>
@@ -1045,7 +1152,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>17</v>
       </c>
@@ -1053,43 +1160,43 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C8" s="14" t="s">
+    <row r="8" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C8" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C10" s="14" t="s">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C10" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C12" s="14" t="s">
+    <row r="12" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C12" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C14" s="14" t="s">
+    <row r="14" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C14" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C16" s="14" t="s">
+    <row r="16" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C16" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C18" s="14" t="s">
+    <row r="18" spans="3:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C18" s="6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1104,52 +1211,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858A08D0-0AC1-41F8-BADB-3F916A563A72}">
   <dimension ref="A1:AH7"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="14" width="9.140625" style="3"/>
+    <col min="3" max="14" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="C2" s="3" t="s">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="C2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="S2">
@@ -1216,7 +1323,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>48</v>
       </c>
@@ -1232,158 +1339,158 @@
       <c r="Y3">
         <v>500</v>
       </c>
-      <c r="Z3" s="2">
+      <c r="Z3" s="1">
         <f>Y3*1.03</f>
         <v>515</v>
       </c>
-      <c r="AA3" s="2">
+      <c r="AA3" s="1">
         <f t="shared" ref="AA3:AH3" si="1">Z3*1.03</f>
         <v>530.45000000000005</v>
       </c>
-      <c r="AB3" s="2">
+      <c r="AB3" s="1">
         <f t="shared" si="1"/>
         <v>546.36350000000004</v>
       </c>
-      <c r="AC3" s="2">
+      <c r="AC3" s="1">
         <f t="shared" si="1"/>
         <v>562.75440500000002</v>
       </c>
-      <c r="AD3" s="2">
+      <c r="AD3" s="1">
         <f t="shared" si="1"/>
         <v>579.63703715000008</v>
       </c>
-      <c r="AE3" s="2">
+      <c r="AE3" s="1">
         <f t="shared" si="1"/>
         <v>597.02614826450008</v>
       </c>
-      <c r="AF3" s="2">
+      <c r="AF3" s="1">
         <f t="shared" si="1"/>
         <v>614.93693271243512</v>
       </c>
-      <c r="AG3" s="2">
+      <c r="AG3" s="1">
         <f t="shared" si="1"/>
         <v>633.38504069380815</v>
       </c>
-      <c r="AH3" s="2">
+      <c r="AH3" s="1">
         <f t="shared" si="1"/>
         <v>652.38659191462239</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>49</v>
       </c>
-      <c r="V4" s="2">
+      <c r="V4" s="1">
         <f>V3*0.7</f>
         <v>70</v>
       </c>
-      <c r="W4" s="2">
+      <c r="W4" s="1">
         <f t="shared" ref="W4:AH4" si="2">W3*0.7</f>
         <v>210</v>
       </c>
-      <c r="X4" s="2">
+      <c r="X4" s="1">
         <f t="shared" si="2"/>
         <v>280</v>
       </c>
-      <c r="Y4" s="2">
+      <c r="Y4" s="1">
         <f t="shared" si="2"/>
         <v>350</v>
       </c>
-      <c r="Z4" s="2">
+      <c r="Z4" s="1">
         <f t="shared" si="2"/>
         <v>360.5</v>
       </c>
-      <c r="AA4" s="2">
+      <c r="AA4" s="1">
         <f t="shared" si="2"/>
         <v>371.315</v>
       </c>
-      <c r="AB4" s="2">
+      <c r="AB4" s="1">
         <f t="shared" si="2"/>
         <v>382.45445000000001</v>
       </c>
-      <c r="AC4" s="2">
+      <c r="AC4" s="1">
         <f t="shared" si="2"/>
         <v>393.92808350000001</v>
       </c>
-      <c r="AD4" s="2">
+      <c r="AD4" s="1">
         <f t="shared" si="2"/>
         <v>405.74592600500006</v>
       </c>
-      <c r="AE4" s="2">
+      <c r="AE4" s="1">
         <f t="shared" si="2"/>
         <v>417.91830378515004</v>
       </c>
-      <c r="AF4" s="2">
+      <c r="AF4" s="1">
         <f t="shared" si="2"/>
         <v>430.45585289870456</v>
       </c>
-      <c r="AG4" s="2">
+      <c r="AG4" s="1">
         <f t="shared" si="2"/>
         <v>443.36952848566568</v>
       </c>
-      <c r="AH4" s="2">
+      <c r="AH4" s="1">
         <f t="shared" si="2"/>
         <v>456.67061434023566</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>50</v>
       </c>
-      <c r="V5" s="2">
+      <c r="V5" s="1">
         <f>V4*0.4</f>
         <v>28</v>
       </c>
-      <c r="W5" s="2">
+      <c r="W5" s="1">
         <f t="shared" ref="W5:AH5" si="3">W4*0.4</f>
         <v>84</v>
       </c>
-      <c r="X5" s="2">
+      <c r="X5" s="1">
         <f t="shared" si="3"/>
         <v>112</v>
       </c>
-      <c r="Y5" s="2">
+      <c r="Y5" s="1">
         <f t="shared" si="3"/>
         <v>140</v>
       </c>
-      <c r="Z5" s="2">
+      <c r="Z5" s="1">
         <f t="shared" si="3"/>
         <v>144.20000000000002</v>
       </c>
-      <c r="AA5" s="2">
+      <c r="AA5" s="1">
         <f t="shared" si="3"/>
         <v>148.52600000000001</v>
       </c>
-      <c r="AB5" s="2">
+      <c r="AB5" s="1">
         <f t="shared" si="3"/>
         <v>152.98178000000001</v>
       </c>
-      <c r="AC5" s="2">
+      <c r="AC5" s="1">
         <f t="shared" si="3"/>
         <v>157.57123340000001</v>
       </c>
-      <c r="AD5" s="2">
+      <c r="AD5" s="1">
         <f t="shared" si="3"/>
         <v>162.29837040200005</v>
       </c>
-      <c r="AE5" s="2">
+      <c r="AE5" s="1">
         <f t="shared" si="3"/>
         <v>167.16732151406003</v>
       </c>
-      <c r="AF5" s="2">
+      <c r="AF5" s="1">
         <f t="shared" si="3"/>
         <v>172.18234115948184</v>
       </c>
-      <c r="AG5" s="2">
+      <c r="AG5" s="1">
         <f t="shared" si="3"/>
         <v>177.34781139426627</v>
       </c>
-      <c r="AH5" s="2">
+      <c r="AH5" s="1">
         <f t="shared" si="3"/>
         <v>182.66824573609426</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>36</v>
       </c>
